--- a/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -72,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +83,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -448,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -544,6 +548,44 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>live, then re-run gen_prod_vs_staging.py with the prod capture wired in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EVERY prod&gt;staging delta is listed (staging has LESS than prod) - spec-intended</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reductions are INCLUDED, annotated 'Per spec - intended reduction? (Yes/No)' with a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>'Spec citation'. The 'No' rows (reductions NOT accounted for in the spec) are the</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>headline release risks. All interim deltas are Yes (spec-declared); No's may appear</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>once live production is captured. See the Summary tab for the per-role Yes/No counts.</t>
         </is>
       </c>
     </row>
@@ -558,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -566,10 +608,12 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,22 +644,32 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Delta (PROD-ONLY / match / staging-more)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Per spec - intended reduction? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Spec citation</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Confidence / Needs-review</t>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Evidence / source</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Confidence (live/spec-predicted/NEEDS-REVIEW)</t>
         </is>
       </c>
     </row>
@@ -652,17 +706,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table (updated-spec-source.md) - Service Manager: 'Loses Invoicing Delete (cannot reverse invoices)'</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Service Manager 'Loses Invoicing Delete (cannot reverse)'</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -699,17 +763,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Service Manager: 'Loses Settings: Service'</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Service Manager 'Loses Settings: Service'</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -746,17 +820,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Service Manager: 'Loses Settings: Parts'</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Service Manager 'Loses Settings: Parts'</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -793,17 +877,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Service Manager: 'Loses Settings: Finance'</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Service Manager 'Loses Settings: Finance'</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -840,17 +934,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Service Manager: 'Loses Settings: Data Import'</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Service Manager 'Loses Settings: Data Import'</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -887,17 +991,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Loses Timesheets Edit'</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Foreman 'Loses Timesheets Edit'</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -934,17 +1048,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Technician: 'Loses Send to Portal'</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Technician 'Lose Send to Portal'; staging Technician is tech-view (button hidden)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -981,17 +1105,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Manager: 'Loses WO Delete'</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Parts Manager 'Loses WO ... Delete'</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1162,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Manager: 'Loses WO Lines Delete'</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Parts Manager 'Loses ... WOL Delete'</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1219,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Office: 'Catalog reduced to View only' (prod Office had Catalog Create&amp;Edit)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Spec Behavior-Changes: Office 'Catalog reduced to V only' (prod Office had Catalog Create&amp;Edit)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>NEEDS REVIEW - prod side unverified (no live prod data)</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
       </c>
     </row>
@@ -1100,15 +1254,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1129,15 +1285,25 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t># spec-predicted PROD-only</t>
+          <t># prod&gt;staging deltas</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t># intended reductions (Yes)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t># NOT-in-spec reductions (No) = RELEASE RISK</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>Highest severity</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Needs-review</t>
         </is>
@@ -1162,12 +1328,18 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1192,12 +1364,18 @@
       <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1222,12 +1400,18 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1252,12 +1436,18 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1282,12 +1472,18 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1312,12 +1508,18 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1342,12 +1544,18 @@
       <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1372,12 +1580,18 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1402,12 +1616,18 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1432,12 +1652,18 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1462,14 +1688,47 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL (all roles)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>NOTE: 'No' (NOT-in-spec) reductions are the headline release risks. They are 0 in this INTERIM because every delta captured so far is a spec-DECLARED reduction (Yes). Live production capture may reveal prod&gt;staging gaps the spec does NOT account for (No) - add them with intended='No', spec_citation='not in spec'.</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3876,7 @@
           <t>Production data NOT captured</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Production could not be authenticated. Missing a valid production sv_sso_session (64-hex). Every prod GET returned 409 'Session has expired'; dev quick-login returns 500 on prod. cf_clearance / Cloudflare is NOT the blocker (409 returns even with no cookies). Host confirmed: SPA app.shopview.com, API api.shopview.com. NEED: a valid production sv_sso_session cookie (and confirmation prod org UUID).</t>
         </is>
@@ -3629,7 +3888,7 @@
           <t>Naming trap</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Legacy 'Service Advisor' -&gt; staging 'Senior Service Advisor' (renamed+expanded); staging 'Service Advisor' comes from legacy 'SA Limited View'. Do NOT match on name.</t>
         </is>
@@ -3641,7 +3900,7 @@
           <t>Spec vs migration-case contradiction</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Section-3549 migration cases C26514/C26515 were authored as 1:1 same-name mappings, contradicting the authoritative spec migration table. NEEDS USER CONFIRMATION which is authoritative for the compare (recommend the spec table).</t>
         </is>
@@ -3653,7 +3912,7 @@
           <t>Prod role inventory unknown</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>The 15 legacy roles are the program-wide catalog; the target prod org may hold a subset and/or shop-specific custom roles. Enumerate live before mapping.</t>
         </is>
@@ -3665,7 +3924,7 @@
           <t>Prod permission representation unknown</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Old-model API shape not yet observed (fe-permissions route 404s on prod). Discover live: GET /api/roles/{id}, /api/auth/me, /api/staff/{id}.</t>
         </is>
@@ -3677,7 +3936,7 @@
           <t>Send-to-Terminal not in spec reduction list</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Send to Terminal (take-payment) is gated in staging on invoicingPaymentsCreateAndEdit AND customerPortalPageAccess. Not on the spec's 'Loses' list; must be diffed live per prod role once prod data is available.</t>
         </is>

--- a/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - DATA STATUS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PROD-ONLY Deltas (spec-pred)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Prod-vs-Staging Deltas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Summary per role" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Staging capability matrix LIVE" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Open questions - NEEDS REVIEW" sheetId="5" state="visible" r:id="rId5"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -557,35 +557,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EVERY prod&gt;staging delta is listed (staging has LESS than prod) - spec-intended</t>
+          <t>BI-DIRECTIONAL: the main tab lists EVERY difference in EITHER direction (one row</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reductions are INCLUDED, annotated 'Per spec - intended reduction? (Yes/No)' with a</t>
+          <t>per staging-role x capability where prod != staging):</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>'Spec citation'. The 'No' rows (reductions NOT accounted for in the spec) are the</t>
+          <t xml:space="preserve">  * STAGING-LESS / PROD-MORE - the role can do MORE in prod than in staging.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>headline release risks. All interim deltas are Yes (spec-declared); No's may appear</t>
+          <t xml:space="preserve">  * STAGING-MORE / PROD-LESS - the new staging model grants MORE than prod has.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>once live production is captured. See the Summary tab for the per-role Yes/No counts.</t>
+          <t>Each row is annotated 'Per spec - intended? (Yes/No)' + 'Spec citation': Yes = the</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>spec documents this change (cited); No = the spec does NOT account for it (release</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>risk). Headline RELEASE RISKS = the 'No' rows in BOTH directions (unaccounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>reductions AND unexpected over-grants). All interim rows are Yes (spec-declared);</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>No's may appear once live production is captured. Summary tab = per-role 2x2 counts.</t>
         </is>
       </c>
     </row>
@@ -600,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -608,8 +636,8 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -644,12 +672,12 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Delta (PROD-ONLY / match / staging-more)</t>
+          <t>Direction (STAGING-LESS / STAGING-MORE)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Per spec - intended reduction? (Yes/No)</t>
+          <t>Per spec - intended? (Yes/No)</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
@@ -701,7 +729,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -758,7 +786,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -815,7 +843,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -872,7 +900,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -929,7 +957,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -986,7 +1014,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1043,7 +1071,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1100,7 +1128,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1157,7 +1185,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1214,7 +1242,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PROD-ONLY</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1238,6 +1266,1887 @@
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Delete a work order</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains WO/WOL/Schedule/PartSales Delete'</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains WO ... Delete'</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Delete a work order line</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains WO/WOL/Schedule/PartSales Delete'</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains ... WOL Delete'</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Delete a schedule entry</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains WO/WOL/Schedule/PartSales Delete'</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains ... Schedule ... Delete'</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Delete a part sale</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains WO/WOL/Schedule/PartSales Delete'</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains ... PartSales Delete'</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vendor &amp; Order Management (full access)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains Vendor FULL'</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains Vendor FULL'</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Invoicing &amp; Payments (full access)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains Invoicing FULL'</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains Invoicing FULL'</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Edit timesheets</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains Timesheets CE'</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains Timesheets CE'</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Customer Portal access</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains Customer Portal'</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains Customer Portal'</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>See AP/AR data</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains AP/AR'</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains AP/AR'</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Service Advisor + SA Technician + SA No Reports</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Reports page access</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Senior SA: 'Gains Reports'; SA No Reports-&gt;SSA: 'Gains Reports'</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Senior SA 'Gains Reports' (also SA No Reports 'Gains Reports')</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Billing Portal access</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Service Manager: 'Gains Billing Portal, Customer Portal'</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Service Manager 'Gains Billing Portal'</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Customer Portal access</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Service Manager: 'Gains Billing Portal, Customer Portal'</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Service Manager 'Gains Customer Portal'</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Delete a work order line</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains WOL Delete'</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains WOL Delete'</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Delete a schedule entry</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Schedule Delete'</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains Schedule Delete'</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>View part sales</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Parts Dept (Part Sales V, Catalog V/CE, Vendor V/CE)'</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains Parts Dept (Part Sales V)'</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>View catalog / inventory</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Parts Dept (... Catalog V/CE ...)'</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains ... Catalog V'</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Create &amp; Edit catalog / inventory items</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Parts Dept (... Catalog V/CE ...)'</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains ... Catalog CE'</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>View vendor &amp; orders</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Parts Dept (... Vendor V/CE)'</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains ... Vendor V'</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Create &amp; Edit vendor &amp; orders</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Parts Dept (... Vendor V/CE)'</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains ... Vendor CE'</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>View invoicing &amp; payments</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Invoicing V/CE'</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains Invoicing V'</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Create &amp; Edit invoicing &amp; payments</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Invoicing V/CE'</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains Invoicing CE'</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Order Parts (WO)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains Order Parts'</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains Order Parts'</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>View History Logs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Foreman: 'Gains History Logs'</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Foreman 'Gains History Logs'</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pick Parts (WO)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Technician: 'Gains Pick Parts'</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Technician 'Gains Pick Parts'</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>View schedule</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Manager: 'Gains Schedule View, Customer Portal'</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Manager 'Gains Schedule View'</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Customer Portal access</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Manager: 'Gains Schedule View, Customer Portal'</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Manager 'Gains Customer Portal'</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pick Parts (WO)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Tech: 'Gains Pick Parts, Order Parts, Invoicing V/CE, History Logs'</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Tech 'Gains Pick Parts'</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Order Parts (WO)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Tech: 'Gains Pick Parts, Order Parts, Invoicing V/CE, History Logs'</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Tech 'Gains Order Parts'</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>View invoicing &amp; payments</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Tech: 'Gains ... Invoicing V/CE ...'</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Tech 'Gains Invoicing V'</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Create &amp; Edit invoicing &amp; payments</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Tech: 'Gains ... Invoicing V/CE ...'</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Tech 'Gains Invoicing CE'</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>View History Logs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Parts Tech: 'Gains ... History Logs'</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Parts Tech 'Gains History Logs'</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Delete a customer (Customer Mgmt full)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - Office: 'Customer Mgmt expanded to FULL (gains Delete)'</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: Office 'Customer Mgmt expanded to FULL (gains Delete)'</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Customer Portal access</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No (SPEC-PREDICTED)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Spec 'Behavior Changes for Migrating Users' table - SA Limited View-&gt;Svc Advisor: 'Gains Customer Portal'</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Spec Behavior-Changes: SA Limited View-&gt;Svc Advisor 'Gains Customer Portal'</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>spec-predicted / NEEDS REVIEW - prod side unverified (no live prod data)</t>
         </is>
@@ -1254,17 +3163,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1285,25 +3195,30 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t># prod&gt;staging deltas</t>
+          <t>Staging-LESS: Yes (intended reduction)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t># intended reductions (Yes)</t>
+          <t>Staging-LESS: No (unaccounted reduction = RISK)</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t># NOT-in-spec reductions (No) = RELEASE RISK</t>
+          <t>Staging-MORE: Yes (intended increase)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Staging-MORE: No (unexpected over-grant = RISK)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Highest severity</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Needs-review</t>
         </is>
@@ -1334,12 +3249,15 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1365,17 +3283,20 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1404,14 +3325,17 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1440,14 +3364,17 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1473,17 +3400,20 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1509,17 +3439,20 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1545,17 +3478,20 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1584,14 +3520,17 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1617,17 +3556,20 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1658,12 +3600,15 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1694,12 +3639,15 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>YES - all prod cells unverified</t>
         </is>
@@ -1717,18 +3665,21 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>NOTE: 'No' (NOT-in-spec) reductions are the headline release risks. They are 0 in this INTERIM because every delta captured so far is a spec-DECLARED reduction (Yes). Live production capture may reveal prod&gt;staging gaps the spec does NOT account for (No) - add them with intended='No', spec_citation='not in spec'.</t>
+          <t>NOTE: the headline RELEASE RISKS are the 'No' columns in BOTH directions - unaccounted reductions (Staging-LESS No) AND unexpected over-grants (Staging-MORE No). Both are 0 in this INTERIM because every delta captured so far is spec-DECLARED (Yes). Live production capture may surface prod!=staging gaps the spec does NOT account for (No) - add them with intended='No', spec_citation='not in spec'.</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -614,36 +614,71 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Service Advisor &amp; Senior Service Advisor rows are flagged NEEDS-REVIEW (mapping</t>
+          <t>MAPPING CONFIRMED by QA lead 2026-07-14 (spec migration table is authoritative):</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  unconfirmed) per the naming trap: legacy 'Service Advisor' -&gt; staging 'Senior SA';</t>
+          <t xml:space="preserve">  Senior Service Advisor &lt;- Service Advisor + SA Technician + SA No Reports (3 merged);</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  staging 'Service Advisor' &lt;- legacy 'SA Limited View'. Computed under the spec map.</t>
+          <t xml:space="preserve">  Service Advisor &lt;- SA Limited View. The naming trap is RESOLVED - these rows are FINAL</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (no longer NEEDS-REVIEW for mapping; a per-capability NEEDS-REVIEW may still apply where</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TABS: 'Deltas - ALL (bi-dir)' whole-app | 'Work Orders - granular' WO-only |</t>
+          <t xml:space="preserve">  an old-model atom has no clean equivalent / is FE-gated).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
+        <is>
+          <t>Administrator compared 1:1 (prod Administrator &lt;-&gt; staging Administrator); the spec's</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  'Owner merged in' is not applicable - no Owner role exists in either environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (confirmed by QA lead 2026-07-14). Administrator delta rows stand as computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TABS: 'Deltas - ALL (bi-dir)' whole-app | 'Work Orders - granular' WO-only |</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Summary tabs (per-role Yes/No 2x2) | Full capability matrix | Open questions.</t>
         </is>
@@ -1864,12 +1899,12 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1956,12 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -1978,12 +2013,12 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2070,12 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2127,12 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2184,12 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2241,12 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2298,12 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2355,12 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2412,12 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2469,12 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - No Reports | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2526,12 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2583,12 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2640,12 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2697,12 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2754,12 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2811,12 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2868,12 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2925,12 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: (none of mapped) | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -2947,12 +2982,12 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3039,12 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3096,12 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3153,12 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -3175,12 +3210,12 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3267,12 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8481,12 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=live | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>live + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8538,12 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA&lt;-&gt;SSA mapping NOT user-confirmed</t>
+          <t>prod holder: Service Advisor - Limited View | staging live | old-&gt;new map conf=NEEDS-REVIEW | SA/SSA merge mapping CONFIRMED by QA lead 2026-07-14</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW + NEEDS-REVIEW (mapping unconfirmed)</t>
+          <t>NEEDS-REVIEW</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11055,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11094,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11098,7 +11133,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11172,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11211,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11215,7 +11250,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11289,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11328,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11367,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11371,7 +11406,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11445,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11602,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11641,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11680,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEEDS-REVIEW</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11719,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11758,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11797,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11836,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11875,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11914,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11953,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -18491,24 +18526,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Service Advisor / Senior SA mapping UNCONFIRMED</t>
+          <t>Service Advisor / Senior SA mapping CONFIRMED (QA lead 2026-07-14)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Naming trap: legacy 'Service Advisor' -&gt; staging 'Senior Service Advisor' (renamed+expanded); staging 'Service Advisor' comes from legacy 'SA Limited View'. Section-3549 migration cases C26514/C26515 were authored as 1:1 same-name mappings, contradicting the spec migration table. All Service-Advisor / Senior-Service-Advisor rows are flagged NEEDS-REVIEW; computed under the spec migration table. CONFIRM which authority governs before treating those deltas as final.</t>
+          <t>Naming trap RESOLVED by QA lead 2026-07-14 (spec migration table is authoritative): staging 'Senior Service Advisor' &lt;- legacy Service Advisor + SA Technician + SA No Reports (3 merged); staging 'Service Advisor' &lt;- legacy 'SA Limited View'. All Service-Advisor / Senior-Service-Advisor rows are FINAL - the mapping-unconfirmed flag is removed. (The section-3549 1:1 same-name migration cases C26514/C26515 are superseded by this ruling.) A per-capability NEEDS-REVIEW may still apply where an old-model atom has no clean equivalent / is FE-gated.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>'Owner' legacy role ABSENT in this prod org</t>
+          <t>Administrator compared 1:1 (Owner not applicable)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Spec migration maps Owner+Administrator -&gt; Admin. The compared prod org (72b2cc90-...) has NO Owner role in GET /api/iam/list-roles (14 legacy roles, not 15). Admin is diffed against Administrator only. If any prod org still has an Owner role, re-run the compare there.</t>
+          <t>Administrator compared 1:1 (prod Administrator &lt;-&gt; staging Administrator); the spec's 'Owner merged in' is not applicable - no Owner role exists in either environment; confirmed by QA lead 2026-07-14. The Administrator delta rows stand as computed from the live Administrator-vs-Administrator capture (not incomplete).</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="READ ME - DATA STATUS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Deltas - ALL (bi-dir)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Work Orders - granular" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary per role (ALL)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary per role (WO)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Out-of-model (staff-record)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Full capability matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Open questions - NEEDS REVIEW" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="!! SUPERSEDED 2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="READ ME - DATA STATUS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Deltas - ALL (bi-dir)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Work Orders - granular" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary per role (ALL)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary per role (WO)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Out-of-model (staff-record)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Full capability matrix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Open questions - NEEDS REVIEW" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,12 @@
       <color rgb="007F3F00"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +81,11 @@
         <fgColor rgb="007F3F00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -89,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +116,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,6 +483,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="118" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>SUPERSEDED — DO NOT RELY ON THIS WORKBOOK (2026-07-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>This workbook presented FE-gated capabilities (Send to Portal / Send to Terminal, etc.) as results that were</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INFERRED from role definitions and source code rather than OBSERVED live in the UI, and its production values</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>were captured in a session that later expired. Per Standing Rules 10 &amp; 12 it is superseded by the observed-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>rebuild:  Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx / .md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correction proven by live observation: Foreman DOES render "Send to Portal" on the WO detail, even though its</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>role lacks the customerPortalPageAccess atom — contradicting this workbook's inference. Kept for history only.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -484,9 +568,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -494,9 +576,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -553,9 +633,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -584,9 +662,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -615,9 +691,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -674,9 +748,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -782,9 +854,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -820,12 +890,8 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-    </row>
+    <row r="54"/>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -917,9 +983,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
@@ -946,7 +1010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9472,7 +9536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12950,675 +13014,6 @@
       <c r="N48" s="4" t="inlineStr">
         <is>
           <t>HIGH - FE-source gate + live role-def verified (staging 2026-07-15)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Per-role 2x2 summary - WHOLE APP (No = release risk; out-of-model excluded)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Staging Role</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Staging role slug</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Merged?</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Prod role(s) mapped</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Migration Type</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>STAGING-LESS intended (Yes)</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>STAGING-LESS NOT-in-spec (No) = RISK</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>STAGING-MORE intended (Yes)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>STAGING-MORE NOT-in-spec (No) = RISK</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Out-of-model (staff-record, excl.)</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Highest severity</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Mapping confirmed?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>administrator</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Direct - Administrator (Owner merge N/A: no Owner in either env)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>service_manager</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Direct (with adjustments)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>senior_service_advisor</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Service Advisor + Service Advisor Technician + Service Advisor - No Reports</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Renamed + expanded (merge: Service Advisor + SA Technician + SA No Reports; gains Reports)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>service_advisor</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Mapped from SA Limited View (AP/AR OFF preserves core restriction)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>foreman</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Direct (with expansions)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>technician</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Direct mapping</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>parts_manager</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Direct (with adjustments)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>parts_technician</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Direct (with expansions)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>office</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Direct (with adjustments)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>sales_representative</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sales Representative + Reporting</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Direct (merge: Sales Representative + Reporting)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>time_clock_user</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Direct mapping</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -13653,7 +13048,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Per-role 2x2 summary - WORK ORDERS only (No = release risk; out-of-model excluded)</t>
+          <t>Per-role 2x2 summary - WHOLE APP (No = release risk; out-of-model excluded)</t>
         </is>
       </c>
     </row>
@@ -13754,15 +13149,15 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
+      <c r="I3" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -13798,16 +13193,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -13852,21 +13247,21 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
+      <c r="G5" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -13902,19 +13297,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -13957,16 +13352,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -14009,7 +13404,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14061,13 +13456,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -14113,16 +13508,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -14162,10 +13557,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14174,7 +13569,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -14223,7 +13618,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -14278,7 +13673,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -14297,6 +13692,675 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Per-role 2x2 summary - WORK ORDERS only (No = release risk; out-of-model excluded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Staging role slug</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Merged?</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Prod role(s) mapped</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Migration Type</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>STAGING-LESS intended (Yes)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>STAGING-LESS NOT-in-spec (No) = RISK</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>STAGING-MORE intended (Yes)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>STAGING-MORE NOT-in-spec (No) = RISK</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Out-of-model (staff-record, excl.)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Highest severity</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Mapping confirmed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Direct - Administrator (Owner merge N/A: no Owner in either env)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>service_manager</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Direct (with adjustments)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>senior_service_advisor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Service Advisor + Service Advisor Technician + Service Advisor - No Reports</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Renamed + expanded (merge: Service Advisor + SA Technician + SA No Reports; gains Reports)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>service_advisor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mapped from SA Limited View (AP/AR OFF preserves core restriction)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>foreman</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Direct (with expansions)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>technician</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Direct mapping</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>parts_manager</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Direct (with adjustments)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>parts_technician</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Direct (with expansions)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Direct (with adjustments)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sales_representative</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sales Representative + Reporting</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct (merge: Sales Representative + Reporting)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>time_clock_user</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Direct mapping</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14845,7 +14909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14938,7 +15002,6 @@
           <t>role slug (live 2026-07-15)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>administrator</t>
@@ -15098,16 +15161,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15135,14 +15193,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15190,10 +15240,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15231,12 +15277,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15274,7 +15314,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15285,9 +15324,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15340,9 +15376,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15395,9 +15428,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15435,12 +15465,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15493,9 +15517,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15548,9 +15569,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15583,17 +15601,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15641,10 +15653,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15692,10 +15700,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15733,7 +15737,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15749,8 +15752,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15798,10 +15799,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15849,10 +15846,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15890,16 +15883,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15937,16 +15925,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15994,10 +15977,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16045,10 +16024,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16086,7 +16061,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16107,7 +16081,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16145,7 +16118,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16166,7 +16138,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16199,17 +16170,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16242,17 +16207,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16290,7 +16249,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16301,9 +16259,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16356,9 +16311,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16396,7 +16348,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16417,7 +16368,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16455,16 +16405,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16502,7 +16447,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16513,9 +16457,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16610,14 +16551,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16675,7 +16608,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16718,12 +16650,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16761,12 +16687,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16829,7 +16749,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16867,7 +16786,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16888,7 +16806,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16911,23 +16828,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16965,7 +16875,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16981,8 +16890,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17020,7 +16927,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17031,9 +16937,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17056,19 +16959,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17106,7 +17001,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17122,8 +17016,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17161,7 +17053,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17172,9 +17063,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17202,9 +17090,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17215,9 +17100,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17255,7 +17137,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17266,9 +17147,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17306,7 +17184,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17327,7 +17204,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17360,8 +17236,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17372,9 +17246,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17402,18 +17273,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17451,7 +17315,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17467,8 +17330,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17506,7 +17367,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17517,9 +17377,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17537,7 +17394,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17548,17 +17404,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17596,8 +17446,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17608,7 +17456,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17641,18 +17488,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17680,15 +17520,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17699,7 +17535,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17732,17 +17567,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17765,19 +17594,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17800,19 +17621,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17830,20 +17643,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17861,20 +17665,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17892,20 +17687,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17923,24 +17709,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17958,24 +17736,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17998,19 +17768,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18048,7 +17810,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18069,7 +17830,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18097,15 +17857,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18116,7 +17872,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18154,7 +17909,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18170,8 +17924,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18194,19 +17946,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n"/>
@@ -18229,7 +17973,6 @@
           <t>PRODUCTION grants (mapped union, live)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>Admin</t>
@@ -18389,12 +18132,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18427,13 +18164,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18476,11 +18206,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18523,11 +18248,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18580,9 +18300,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18640,8 +18357,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18699,8 +18414,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18753,9 +18466,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18808,9 +18518,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18853,11 +18560,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18875,7 +18577,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18886,8 +18587,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18898,9 +18597,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18918,7 +18614,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18929,8 +18624,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18941,9 +18634,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18961,7 +18651,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18982,15 +18671,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19008,7 +18693,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19024,16 +18708,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19046,8 +18725,6 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19068,11 +18745,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19115,11 +18787,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19157,12 +18824,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19200,12 +18861,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19248,11 +18903,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19295,11 +18945,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19337,7 +18982,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19358,7 +19002,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19391,8 +19034,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19408,8 +19049,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19509,8 +19148,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19521,9 +19158,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19581,8 +19215,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19635,9 +19267,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19675,9 +19304,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19688,7 +19314,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19731,15 +19356,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19772,8 +19393,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19784,9 +19403,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19886,13 +19502,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19935,14 +19544,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19985,12 +19591,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20028,12 +19628,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20076,8 +19670,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20088,7 +19680,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20126,9 +19717,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20139,7 +19727,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20157,7 +19744,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20168,17 +19754,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20216,7 +19796,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20232,8 +19811,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20251,7 +19828,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20262,8 +19838,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20279,8 +19853,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20298,7 +19870,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20309,21 +19880,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -20381,8 +19947,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20415,8 +19979,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20432,8 +19994,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20466,8 +20026,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20483,8 +20041,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20517,8 +20073,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20534,8 +20088,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20593,8 +20145,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20637,11 +20187,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20659,7 +20204,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20670,13 +20214,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20709,8 +20246,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20726,8 +20261,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20760,8 +20293,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20772,9 +20303,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20807,8 +20335,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20819,9 +20345,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20844,19 +20367,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20879,15 +20394,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20910,16 +20416,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20930,7 +20431,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20943,17 +20443,6 @@
           <t>GEN</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -20971,7 +20460,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20982,17 +20470,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -21010,7 +20492,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21021,17 +20502,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21049,7 +20524,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21060,17 +20534,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21088,24 +20556,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21123,7 +20583,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21134,17 +20593,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21177,17 +20630,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21205,20 +20652,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21236,24 +20674,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21286,8 +20716,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21308,7 +20736,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21341,8 +20768,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21358,8 +20783,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21377,7 +20800,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21393,16 +20815,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21420,31 +20837,23 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-Permission-Gaps_2026-07-14.xlsx
@@ -64,7 +64,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +123,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,62 +489,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>SUPERSEDED 2026-07-15 — this workbook contained INFERENCE-TAINTED FE-gated results. Use Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx (observed-only). Do not rely on this file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>SUPERSEDED — DO NOT RELY ON THIS WORKBOOK (2026-07-15)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>This workbook presented FE-gated capabilities (Send to Portal / Send to Terminal, etc.) as results that were</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INFERRED from role definitions and source code rather than OBSERVED live in the UI, and its production values</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>INFERRED from role definitions and source code rather than OBSERVED live in the UI, and its production values</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>were captured in a session that later expired. Per Standing Rules 10 &amp; 12 it is superseded by the observed-only</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>rebuild:  Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx / .md</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Correction proven by live observation: Foreman DOES render "Send to Portal" on the WO detail, even though its</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Correction proven by live observation: Foreman DOES render "Send to Portal" on the WO detail, even though its</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>role lacks the customerPortalPageAccess atom — contradicting this workbook's inference. Kept for history only.</t>
         </is>
@@ -568,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -576,7 +584,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -633,7 +640,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -662,7 +668,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -691,7 +696,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -748,7 +752,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -854,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -890,8 +892,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -983,7 +983,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
